--- a/AAII_Financials/Quarterly/ECAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ECAT_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
   <si>
     <t>ECAT</t>
   </si>
@@ -656,45 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -713,23 +714,26 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>28100</v>
+      </c>
+      <c r="E8" s="3">
         <v>31200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>23300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>19400</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
       </c>
@@ -748,23 +752,26 @@
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E9" s="3">
         <v>11100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12100</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,23 +790,26 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>16800</v>
+      </c>
+      <c r="E10" s="3">
         <v>20100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>12100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>7300</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
       </c>
@@ -818,8 +828,11 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -833,8 +846,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -868,8 +882,11 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -903,8 +920,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -938,8 +958,11 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -973,8 +996,11 @@
       <c r="M15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -985,23 +1011,24 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E17" s="3">
         <v>11900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>12400</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,23 +1047,26 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E18" s="3">
         <v>19300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>11900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7000</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1055,8 +1085,11 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,23 +1103,24 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>64400</v>
+      </c>
+      <c r="E20" s="3">
         <v>194800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>13700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-345600</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1105,8 +1139,11 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1140,8 +1177,11 @@
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1175,23 +1215,26 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E23" s="3">
         <v>214200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>25600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-338500</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1210,8 +1253,11 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1245,8 +1291,11 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1280,23 +1329,26 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E26" s="3">
         <v>214200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>25600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-338500</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1315,23 +1367,26 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E27" s="3">
         <v>214200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>25600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-338500</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1350,8 +1405,11 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1385,8 +1443,11 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1420,8 +1481,11 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1455,8 +1519,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1490,23 +1557,26 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-64400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-194800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-13700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>345600</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1525,23 +1595,26 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E33" s="3">
         <v>214200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>25600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-338500</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1560,8 +1633,11 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1595,23 +1671,26 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E35" s="3">
         <v>214200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>25600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-338500</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1630,28 +1709,31 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1670,8 +1752,11 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1685,8 +1770,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1700,23 +1786,24 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>200</v>
+      </c>
+      <c r="E41" s="3">
         <v>500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3100</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,8 +1822,11 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1770,23 +1860,26 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E43" s="3">
         <v>21100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>25700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24400</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1805,8 +1898,11 @@
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1840,13 +1936,16 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -1854,8 +1953,8 @@
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+      <c r="G45" s="3">
+        <v>0</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1875,8 +1974,11 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1910,23 +2012,26 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1936600</v>
+      </c>
+      <c r="E47" s="3">
         <v>1960100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1879500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1762500</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,8 +2050,11 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1980,8 +2088,11 @@
       <c r="M48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2015,8 +2126,11 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2050,8 +2164,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2085,8 +2202,11 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2120,8 +2240,11 @@
       <c r="M52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2155,23 +2278,26 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1977800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2009600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2026100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1814600</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2190,8 +2316,11 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2205,8 +2334,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2220,23 +2350,24 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E57" s="3">
         <v>151700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>216000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>8600</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2255,23 +2386,26 @@
       <c r="M57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E58" s="3">
         <v>2200</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>11100</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2290,23 +2424,26 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4900</v>
+        <v>2300</v>
       </c>
       <c r="E59" s="3">
         <v>4900</v>
       </c>
       <c r="F59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G59" s="3">
         <v>5700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,8 +2462,11 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2360,8 +2500,11 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2395,8 +2538,11 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2430,8 +2576,11 @@
       <c r="M62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2465,8 +2614,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2500,8 +2652,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2535,23 +2690,26 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>139200</v>
+      </c>
+      <c r="E66" s="3">
         <v>167800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>324200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47700</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2570,8 +2728,11 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2585,8 +2746,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2620,8 +2782,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2655,8 +2820,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2690,8 +2858,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2725,23 +2896,26 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-160300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-300200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-328400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,8 +2934,11 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2795,8 +2972,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2830,8 +3010,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2865,23 +3048,26 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1838700</v>
+      </c>
+      <c r="E76" s="3">
         <v>1841800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1701900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1766900</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2900,8 +3086,11 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2935,28 +3124,31 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2975,23 +3167,26 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>80800</v>
+      </c>
+      <c r="E81" s="3">
         <v>214200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>25600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-338500</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3010,8 +3205,11 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3025,8 +3223,9 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3060,8 +3259,11 @@
       <c r="M83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3297,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3130,8 +3335,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3165,8 +3373,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3200,8 +3411,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3235,23 +3449,26 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>86300</v>
+      </c>
+      <c r="E89" s="3">
         <v>79300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>98600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>87300</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3487,11 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3285,8 +3505,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3320,8 +3541,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3355,8 +3579,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3390,8 +3617,11 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3425,8 +3655,11 @@
       <c r="M94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3440,23 +3673,24 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-77700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-74100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-62500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-63300</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
@@ -3475,8 +3709,11 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3510,8 +3747,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3545,8 +3785,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3580,23 +3823,26 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-85000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-75800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-94100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-77300</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3615,8 +3861,11 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3629,8 +3878,8 @@
       <c r="F101" s="3">
         <v>0</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
+      <c r="G101" s="3">
+        <v>0</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3650,23 +3899,26 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E102" s="3">
         <v>3500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>4500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10000</v>
       </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3683,6 +3935,9 @@
         <v>3</v>
       </c>
       <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ECAT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ECAT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="92">
   <si>
     <t>ECAT</t>
   </si>
@@ -656,49 +656,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -717,26 +718,29 @@
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E8" s="3">
         <v>28100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>31200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>19400</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -755,26 +759,29 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E9" s="3">
         <v>11300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12100</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -793,26 +800,29 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E10" s="3">
         <v>16800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>12100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>7300</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -831,8 +841,11 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,8 +860,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -885,8 +899,11 @@
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -923,31 +940,34 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -961,8 +981,11 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -999,8 +1022,11 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1012,26 +1038,27 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E17" s="3">
         <v>11700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>11900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12400</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1050,26 +1077,29 @@
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E18" s="3">
         <v>16400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>19300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>11900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7000</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1088,8 +1118,11 @@
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1104,26 +1137,27 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>160000</v>
+      </c>
+      <c r="E20" s="3">
         <v>64400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>194800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>13700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-345600</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,8 +1176,11 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1180,8 +1217,11 @@
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1218,26 +1258,29 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E23" s="3">
         <v>80800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>214200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>25600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-338500</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1256,8 +1299,11 @@
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1294,8 +1340,11 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1332,26 +1381,29 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E26" s="3">
         <v>80800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>214200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>25600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-338500</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1370,26 +1422,29 @@
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E27" s="3">
         <v>80800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>214200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>25600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-338500</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1408,8 +1463,11 @@
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1446,8 +1504,11 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1484,8 +1545,11 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1522,8 +1586,11 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1560,26 +1627,29 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-160000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-64400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-194800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-13700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>345600</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1598,26 +1668,29 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E33" s="3">
         <v>80800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>214200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>25600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-338500</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1636,8 +1709,11 @@
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1674,26 +1750,29 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E35" s="3">
         <v>80800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>214200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>25600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-338500</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1712,31 +1791,34 @@
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1755,8 +1837,11 @@
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1771,8 +1856,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1787,26 +1873,27 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
         <v>200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3100</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1825,8 +1912,11 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1863,26 +1953,29 @@
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E43" s="3">
         <v>13300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>21100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>25700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24400</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1901,8 +1994,11 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1939,25 +2035,28 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>400</v>
       </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
       <c r="F45" s="3">
         <v>0</v>
       </c>
       <c r="G45" s="3">
         <v>0</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>0</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
@@ -1977,8 +2076,11 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2015,26 +2117,29 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2031200</v>
+      </c>
+      <c r="E47" s="3">
         <v>1936600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1960100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1879500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1762500</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2053,8 +2158,11 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2091,8 +2199,11 @@
       <c r="N48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2129,8 +2240,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2167,8 +2281,11 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2205,8 +2322,11 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2243,8 +2363,11 @@
       <c r="N52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2281,26 +2404,29 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2067300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1977800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2009600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2026100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1814600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2319,8 +2445,11 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2335,8 +2464,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2351,26 +2481,27 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E57" s="3">
         <v>124800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>151700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>216000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>8600</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2389,26 +2520,29 @@
       <c r="N57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E58" s="3">
         <v>7500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2200</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>11100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2427,26 +2561,29 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E59" s="3">
         <v>2300</v>
-      </c>
-      <c r="E59" s="3">
-        <v>4900</v>
       </c>
       <c r="F59" s="3">
         <v>4900</v>
       </c>
       <c r="G59" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H59" s="3">
         <v>5700</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,8 +2602,11 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2503,8 +2643,11 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2541,8 +2684,11 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2579,8 +2725,11 @@
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2617,8 +2766,11 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2655,8 +2807,11 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2693,26 +2848,29 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>155300</v>
+      </c>
+      <c r="E66" s="3">
         <v>139200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>167800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>324200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47700</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2731,8 +2889,11 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2747,8 +2908,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2785,8 +2947,11 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2823,8 +2988,11 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2861,8 +3029,11 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2899,26 +3070,29 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-41200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-160300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-300200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-328400</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2937,8 +3111,11 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2975,8 +3152,11 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3013,8 +3193,11 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3051,26 +3234,29 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1912000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1838700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1841800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1701900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1766900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3089,8 +3275,11 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3127,31 +3316,34 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3170,26 +3362,29 @@
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E81" s="3">
         <v>80800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>214200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>25600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-338500</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3208,8 +3403,11 @@
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3224,8 +3422,9 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3262,8 +3461,11 @@
       <c r="N83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3300,8 +3502,11 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3338,8 +3543,11 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3376,8 +3584,11 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3414,8 +3625,11 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3452,26 +3666,29 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>109400</v>
+      </c>
+      <c r="E89" s="3">
         <v>86300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>79300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>98600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>87300</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3490,8 +3707,11 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3506,8 +3726,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3544,8 +3765,11 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3582,8 +3806,11 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3620,8 +3847,11 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -3658,8 +3888,11 @@
       <c r="N94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3674,26 +3907,27 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-77700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-74100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-62500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-63300</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
@@ -3712,8 +3946,11 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3750,8 +3987,11 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3788,8 +4028,11 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3826,26 +4069,29 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-104500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-85000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-75800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-94100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-77300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3864,8 +4110,11 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3881,8 +4130,8 @@
       <c r="G101" s="3">
         <v>0</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
+      <c r="H101" s="3">
+        <v>0</v>
       </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
@@ -3902,26 +4151,29 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10000</v>
       </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I102" s="3" t="s">
         <v>3</v>
       </c>
@@ -3938,6 +4190,9 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
